--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-005_Cografya_12_Sinif_Secmeli_4_Saat_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-005_Cografya_12_Sinif_Secmeli_4_Saat_Yillik_Plani_v1.0.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.SINIF 4 SAAT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Açıklamalar ve Onay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'12.SINIF 4 SAAT'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Açıklamalar ve Onay'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -539,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -2069,162 +2071,234 @@
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="H35:H36"/>
+  </mergeCells>
+  <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LGNL-CYP-CP-005 · okulapp.org&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.3" customWidth="1" min="1" max="1"/>
+    <col width="9.01" customWidth="1" min="2" max="2"/>
+    <col width="4.77" customWidth="1" min="3" max="3"/>
+    <col width="12.72" customWidth="1" min="4" max="4"/>
+    <col width="20.14" customWidth="1" min="5" max="5"/>
+    <col width="27.56" customWidth="1" min="6" max="6"/>
+    <col width="44.52" customWidth="1" min="7" max="7"/>
+    <col width="13.25" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>[OKUL ADI]</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 2026-2027 EĞİTİM ÖĞRETİM YILI 12. SINIF SEÇMELİ COĞRAFYA DERSİ (HAFTADA 4 SAAT) YILLIK PLANI — AÇIKLAMALAR VE ONAY</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>GENEL AÇIKLAMALAR (çerçeve plandan)</t>
         </is>
       </c>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-    </row>
-    <row r="58" ht="66.59999999999999" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="66.59999999999999" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Ölçme ve değerlendirme: Ölçme ve değerlendirme yöntemleri kazanımın düzeyi, konu içeriği dikkate alınarak planlanmalıdır. Kazanıma ve konunun içeriğine uygun olarak belirlenen bu ölçme ve değerlendirme yöntemlerinden klasik ve tamamlayıcı (alternatif) ölçme ve değerlendirme yöntemleri birlikte kullanılarak öğrencinin bütüncül olarak değerlendirilmesi sağlanmalıdır. Ölçme ve değerlendirme çalışmalarında sadece sonuca odaklı değerlendirme yapılmamalı süreç değerlendirmeye yönelik ölçme etkinlikleri de planlanmalıdır, süreçte planlanan değerlendirmeler öğretimde ve öğrenmelerde bir eksiklik olup olmadığının tespit edilmesi ve giderilmesinde önemlidir. Kaynaştırma/Bütünleştirme yoluyla eğitim ve öğretimlerine devam eden öğrencilere yönelik ölçme değerlendirmede Bireyselleştirilmiş Eğitim Programı (BEP) esas alınır.</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="56" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Yöntem ve teknikler: Yöntem ve teknikler seçilirken kazanım, öğrenci özellikleri (hazırbulunuşluk düzeyleri, öğrenme stilleri, ilgi alanları vb.), öğretmenin ve konunun özellikleri, materyaller, maliyet, zaman, sınıf mevcudu ve okul türü farklılığı dikkate alınması gerekir. Öğretim sürecinde yer alan okul dışı öğrenme etkinlikleri, ders yılı başı okul zümre öğretmenleri toplantısında belirlenecektir. Seçilen yöntem ve tekniklere uygun olarak ölçme ve değerlendirme faaliyetlerinin de yapılandırılması eşgüdümlü bir şekilde yapılmalıdır. Öğrenme süreçlerinde değerlendirme faaliyetleri mümkün olduğu kadar süreci değerlendirecek biçimde tasarlanmalıdır.</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="13.6" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="13.6" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Okul dışı öğrenme: Okul dışı öğrenme etkinlikleri, ders yılı başı okul zümre öğretmenleri toplantısında belirlenecektir.</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>OKUL UYARLAMA NOTLARI</t>
         </is>
       </c>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="10" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="10" t="n"/>
-      <c r="H62" s="10" t="n"/>
-    </row>
-    <row r="63" ht="24.2" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="24.2" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>GENEL ŞABLON: Bu plan, okulapp.org belge arşivinde yayımlanan genel sürümdür (CC BY 4.0). Köşeli parantezli KIRMIZI alanlar (okul adı, ad-soyad, tarih) okulun bilgileriyle doldurulur; doldurduktan sonra parantez kaldırılır ve yazı rengi siyaha çevrilir.</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="34.8" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="34.8" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak yıllık planının "12.SINIF 4 SAAT" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ölçme ve değerlendirme, yöntem-teknik ve okul dışı öğrenme genel açıklamaları haftalık çizelgenin altındaki bölüme taşınmıştır.</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="45.4" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="45.4" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-    </row>
-    <row r="66" ht="24.2" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="24.2" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>OKUL TEMELLİ PLANLAMA: 2018 Coğrafya Dersi Öğretim Programında okul temelli planlama süresi bulunmaz. Okul dışı öğrenme etkinlikleri, aşağıdaki genel açıklama uyarınca ders yılı başı zümre toplantısında planlanır.</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-    </row>
-    <row r="67" ht="13.6" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="13.6" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
-    </row>
-    <row r="68" ht="13.6" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="13.6" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
-    </row>
-    <row r="70" ht="24.2" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="16" ht="24.2" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bu yıllık plan, Eğitim ve Öğretim Çalışmalarının Planlı Yürütülmesine İlişkin Yönergenin 9 uncu ve 10 uncu maddeleri uyarınca coğrafya zümre öğretmenlerince ortak hazırlanarak okul müdürlüğüne sunulmuştur. Tarih: </t>
@@ -2239,202 +2313,191 @@
           </r>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-    </row>
-    <row r="72" ht="13" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Adı Soyadı</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Görevi</t>
         </is>
       </c>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>İmza</t>
         </is>
       </c>
-      <c r="H72" s="10" t="n"/>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
         </is>
       </c>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="2" t="n"/>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="2" t="n"/>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F75" s="2" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="2" t="n"/>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="2" t="n"/>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n"/>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F77" s="2" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="2" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>UYGUNDUR</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>[../09/2026]</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="15" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Okul Müdürü</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B35:B36"/>
+  <mergeCells count="35">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-005_Cografya_12_Sinif_Secmeli_4_Saat_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-005_Cografya_12_Sinif_Secmeli_4_Saat_Yillik_Plani_v1.0.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -1981,106 +1981,13 @@
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="n"/>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="n"/>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C46:C47"/>
     <mergeCell ref="D46:H46"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="B35:B36"/>

--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-005_Cografya_12_Sinif_Secmeli_4_Saat_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-005_Cografya_12_Sinif_Secmeli_4_Saat_Yillik_Plani_v1.0.xlsx
@@ -2012,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -2134,10 +2134,10 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
     </row>
-    <row r="10" ht="34.8" customHeight="1">
+    <row r="10" ht="45.4" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak yıllık planının "12.SINIF 4 SAAT" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ölçme ve değerlendirme, yöntem-teknik ve okul dışı öğrenme genel açıklamaları haftalık çizelgenin altındaki bölüme taşınmıştır.</t>
+          <t>ÖĞRETİM PROGRAMI: Bu plan, Talim ve Terbiye Kurulunun 19.01.2018 tarihli ve 26 sayılı kararıyla kabul edilen Coğrafya Dersi Öğretim Programına göre hazırlanmıştır. Türkiye Yüzyılı Maarif Modeli Coğrafya Dersi Öğretim Programı, Kurulun 13.05.2026 tarihli ve 53 sayılı kararı uyarınca 12. sınıf seviyesinde 2027-2028 eğitim ve öğretim yılında uygulanacaktır; bu nedenle 2026-2027'de 12. sınıfta 2018 programı yürürlüktedir. Programın iki ve dört ders saatlik bölümleri ayrıdır; bu plan kendi bölümüne göre hazırlanmıştır.</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -2148,10 +2148,10 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
     </row>
-    <row r="11" ht="45.4" customHeight="1">
+    <row r="11" ht="34.8" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
+          <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak yıllık planının "12.SINIF 4 SAAT" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ölçme ve değerlendirme, yöntem-teknik ve okul dışı öğrenme genel açıklamaları haftalık çizelgenin altındaki bölüme taşınmıştır.</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -2162,10 +2162,10 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
     </row>
-    <row r="12" ht="24.2" customHeight="1">
+    <row r="12" ht="45.4" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>OKUL TEMELLİ PLANLAMA: 2018 Coğrafya Dersi Öğretim Programında okul temelli planlama süresi bulunmaz. Okul dışı öğrenme etkinlikleri, aşağıdaki genel açıklama uyarınca ders yılı başı zümre toplantısında planlanır.</t>
+          <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -2176,10 +2176,10 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
     </row>
-    <row r="13" ht="13.6" customHeight="1">
+    <row r="13" ht="24.2" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
+          <t>OKUL TEMELLİ PLANLAMA: 2018 Coğrafya Dersi Öğretim Programında okul temelli planlama süresi bulunmaz. Okul dışı öğrenme etkinlikleri, aşağıdaki genel açıklama uyarınca ders yılı başı zümre toplantısında planlanır.</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -2193,7 +2193,7 @@
     <row r="14" ht="13.6" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
+          <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -2204,8 +2204,22 @@
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
     </row>
-    <row r="16" ht="24.2" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="15" ht="13.6" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="17" ht="24.2" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bu yıllık plan, Eğitim ve Öğretim Çalışmalarının Planlı Yürütülmesine İlişkin Yönergenin 9 uncu ve 10 uncu maddeleri uyarınca coğrafya zümre öğretmenlerince ortak hazırlanarak okul müdürlüğüne sunulmuştur. Tarih: </t>
@@ -2220,53 +2234,35 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Adı Soyadı</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Görevi</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>İmza</t>
         </is>
       </c>
-      <c r="H18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>[Adı SOYADI]</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -2279,7 +2275,7 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Coğrafya Öğretmeni</t>
+          <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
@@ -2340,40 +2336,60 @@
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="2" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>[Adı SOYADI]</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Coğrafya Öğretmeni</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>UYGUNDUR</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>[../09/2026]</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Okul Müdürü</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="A11:H11"/>
@@ -2382,28 +2398,27 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="E18:F18"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
